--- a/Material_Didactico/RESUMEN EXAMENES/INSTRUCCIONES.xlsx
+++ b/Material_Didactico/RESUMEN EXAMENES/INSTRUCCIONES.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DAW\DECROLY\Programacion\practicas_programacion\Material_Didactico\RESUMEN EXAMENES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C214F3C-DBC1-42AF-A6C1-1AE9B3A9A131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F3BAC8-5E6F-40CF-9C9C-B70CE2BFB727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{27C2CB54-7F10-4955-AE76-3C00B0E9FCF6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{27C2CB54-7F10-4955-AE76-3C00B0E9FCF6}"/>
   </bookViews>
   <sheets>
     <sheet name="GENERAL" sheetId="1" r:id="rId1"/>
     <sheet name="ARRAYS" sheetId="2" r:id="rId2"/>
+    <sheet name="LISTAS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="77">
   <si>
     <t>Bloque</t>
   </si>
@@ -408,6 +409,354 @@
   </si>
   <si>
     <t>lista.remove(objeto);</t>
+  </si>
+  <si>
+    <t>Estructura</t>
+  </si>
+  <si>
+    <t>List&lt;Heroe&gt; lista = new ArrayList&lt;&gt;();</t>
+  </si>
+  <si>
+    <t>HashSet</t>
+  </si>
+  <si>
+    <t>HashMap</t>
+  </si>
+  <si>
+    <t>Map&lt;String, Heroe&gt; mapa = new HashMap&lt;&gt;();</t>
+  </si>
+  <si>
+    <t>Cuándo usarla (Palabras clave)</t>
+  </si>
+  <si>
+    <t>Declaración e Instanciación</t>
+  </si>
+  <si>
+    <t>Operaciones de Gestión (Qué haces después)</t>
+  </si>
+  <si>
+    <t>"Lista de...", "Listar todos", "Orden de llegada".</t>
+  </si>
+  <si>
+    <r>
+      <t>Añadir:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>lista.add(obj);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Borrar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>lista.remove(index);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Buscar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Bucle </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Listar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>for (Heroe h : lista)</t>
+    </r>
+  </si>
+  <si>
+    <t>"Buscar por ID/DNI", "Clave-Valor", "Búsqueda rápida".</t>
+  </si>
+  <si>
+    <r>
+      <t>Añadir:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>mapa.put(dni, obj);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Borrar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>mapa.remove(dni);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Buscar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>mapa.get(dni);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Directo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Listar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>for (Heroe h : mapa.values())</t>
+    </r>
+  </si>
+  <si>
+    <t>"No duplicados", "DNI único", "Sin orden".</t>
+  </si>
+  <si>
+    <t>Set&lt;String&gt; set = new HashSet&lt;&gt;();</t>
+  </si>
+  <si>
+    <r>
+      <t>Añadir:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>set.add(dato);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Borrar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>set.remove(dato);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Buscar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>set.contains(dato);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Listar:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>for (String s : set)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -449,15 +798,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -576,11 +931,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
@@ -632,6 +1039,51 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,27 +1092,33 @@
   <dxfs count="15">
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="0"/>
+        <color rgb="FF1F1F1F"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -686,12 +1144,14 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -724,61 +1184,24 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
-    </dxf>
-    <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -793,18 +1216,77 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -830,14 +1312,12 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -870,10 +1350,8 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -883,37 +1361,12 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -940,6 +1393,9 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
@@ -948,22 +1404,18 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF1F1F1F"/>
+        <color theme="0"/>
         <name val="Arial"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -995,24 +1447,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{340134E4-EA96-4C8C-8F91-DF54AF0CE873}" name="Tabla2" displayName="Tabla2" ref="B5:E16" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{340134E4-EA96-4C8C-8F91-DF54AF0CE873}" name="Tabla2" displayName="Tabla2" ref="B5:E16" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="B5:E16" xr:uid="{340134E4-EA96-4C8C-8F91-DF54AF0CE873}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D5717DA1-E73B-43ED-81AE-0BC51B3B0F3D}" name="Bloque" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{B0421C87-836E-4FE6-901C-2E0904426C74}" name="Herramienta" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{4A8527FD-2E66-4B29-A473-1EA985F1CAE1}" name="Código de Referencia Rápida" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{BCF6000F-D827-4FF3-8649-84F4BA2997F7}" name="Uso en el Examen 💡" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{D5717DA1-E73B-43ED-81AE-0BC51B3B0F3D}" name="Bloque" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{B0421C87-836E-4FE6-901C-2E0904426C74}" name="Herramienta" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{4A8527FD-2E66-4B29-A473-1EA985F1CAE1}" name="Código de Referencia Rápida" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{BCF6000F-D827-4FF3-8649-84F4BA2997F7}" name="Uso en el Examen 💡" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{57CC794F-21CE-49A7-AAB8-FE831BC00F3C}" name="Tabla3" displayName="Tabla3" ref="B6:C10" totalsRowShown="0" headerRowDxfId="0" dataDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{57CC794F-21CE-49A7-AAB8-FE831BC00F3C}" name="Tabla3" displayName="Tabla3" ref="B6:C10" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B6:C10" xr:uid="{57CC794F-21CE-49A7-AAB8-FE831BC00F3C}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{8034B251-9253-49D3-9C6E-077F5971AA7A}" name="Acción" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{EA63A2C8-A927-415F-8DC9-A9A6342261C2}" name="Código 🔧" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8034B251-9253-49D3-9C6E-077F5971AA7A}" name="Acción" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{EA63A2C8-A927-415F-8DC9-A9A6342261C2}" name="Código 🔧" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1575,4 +2027,161 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811658F8-AD28-4CFA-A1AE-0A595F04284F}">
+  <dimension ref="C4:F17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" customWidth="1"/>
+    <col min="5" max="5" width="44.6640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="31.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:6" ht="15" thickBot="1"/>
+    <row r="5" spans="3:6" ht="28.2" thickBot="1">
+      <c r="C5" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" ht="18" customHeight="1">
+      <c r="C6" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" ht="18" customHeight="1">
+      <c r="C7" s="22"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" ht="18" customHeight="1">
+      <c r="C8" s="22"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" ht="18" customHeight="1" thickBot="1">
+      <c r="C9" s="23"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6">
+      <c r="C10" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6">
+      <c r="C11" s="22"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6">
+      <c r="C12" s="22"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" ht="27.6" thickBot="1">
+      <c r="C13" s="23"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6">
+      <c r="C14" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6">
+      <c r="C15" s="22"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="19" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6">
+      <c r="C16" s="22"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" ht="15" thickBot="1">
+      <c r="C17" s="23"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E10:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>